--- a/docs/db/ezEKP Java 근태관리 테이블 정의서.xlsx
+++ b/docs/db/ezEKP Java 근태관리 테이블 정의서.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NC370\Desktop\근태관리\근태관리 개발\산출물\DB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NC370\Desktop\근태관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="용어사전" sheetId="2" r:id="rId1"/>
     <sheet name="단어사전" sheetId="3" r:id="rId2"/>
-    <sheet name="테이블정의서" sheetId="5" r:id="rId3"/>
+    <sheet name="테이블정의서(기존)" sheetId="5" r:id="rId3"/>
+    <sheet name="테이블정의서(연차관리)" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="658">
   <si>
     <t>근무종료시간</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1719,12 +1720,609 @@
     <t>아이콘 이미지 이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>테이블 이름</t>
+  </si>
+  <si>
+    <t>tbl_attitude_annual</t>
+  </si>
+  <si>
+    <t>테이블 설명</t>
+  </si>
+  <si>
+    <t>연차 정보</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRIMARY KEY</t>
+  </si>
+  <si>
+    <t>user_id, tenant_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>FOREIGN KEY</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>INDEX</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <t>컬럼 이름</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>참조 테이블</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>VARCHAR(80)</t>
+  </si>
+  <si>
+    <t>annual_holiday_cnt</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 연차 수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>join_date</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>company_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEDIUMINT(5)</t>
+  </si>
+  <si>
+    <t>테넌트ID</t>
+  </si>
+  <si>
+    <t>tbl_attitude_annual_history</t>
+  </si>
+  <si>
+    <t>연차 수정 기록</t>
+  </si>
+  <si>
+    <t>annual_history_id</t>
+  </si>
+  <si>
+    <t>INT(20)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차수정기록ID</t>
+  </si>
+  <si>
+    <t>origin_annual_cnt</t>
+  </si>
+  <si>
+    <t>기존연차수</t>
+  </si>
+  <si>
+    <t>change_annual_cnt</t>
+  </si>
+  <si>
+    <t>수정연차수</t>
+  </si>
+  <si>
+    <t>change_reason</t>
+  </si>
+  <si>
+    <t>VARCHAR(2000)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정사유</t>
+  </si>
+  <si>
+    <t>change_date</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
+  </si>
+  <si>
+    <t>수정일자</t>
+  </si>
+  <si>
+    <t>change_user_id</t>
+  </si>
+  <si>
+    <t>수정자ID</t>
+  </si>
+  <si>
+    <t>VARCHAR(200)</t>
+  </si>
+  <si>
+    <t>회사ID</t>
+  </si>
+  <si>
+    <t>tbl_attitude_annual_conf</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>회사ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenant_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR(1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차자동발생</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차발생기준</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>initial_date</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>잔여연차음수허용여부</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_annual_tmnt</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BIGINT(20)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>근태ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>appl_cnt</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>writer_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자이름</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자이름2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>writer_title</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(200)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자직위2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(80)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>writer_dept_name2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>delflag</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>appr_date</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATETIME</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>승인상태</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>content</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>appr_user_name2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>appl_date</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정저장일시</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tbl_attitude_apr_conn</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차연동문서ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>취소연동문서ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>annual_appr_status</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차결재상태</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>monthly_holiday_cnt</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL(3,1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>월차 수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL(3,1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차 수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>additional_holiday_cnt</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL(3,1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>입사일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL(3,1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL(3,1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차 설정 관리</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>company_id, tenant_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>테넌트ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>annual_cancel_rule</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차취소방식</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_annual_auto_gnrt</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>annual_gnrt_std</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>회계연도 기산일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_minus_annual</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR(1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR(1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차소멸여부</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>round_off_rule</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>소수점처리</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>config_set_date</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tbl_attitude_annual_canappl</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차 취소 관리</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>attitude_id, appl_cnt, company_id, tenant_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>attitude_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT(11)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정신청키</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(80)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>테넌트ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(80)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>writer_name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>writer_name2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(200)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자직위</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>writer_title2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>writer_dept_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자부서ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>writer_dept_name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자부서이름</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자부서이름2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>appr_user_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>승인자ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>승인일시</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>appr_status</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(3000)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>appr_user_name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>승인자이름</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>승인자이름2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>연차 결재 연동</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>attitude_id, company_id, tenant_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사원ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>annual_doc_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(80)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cancel_doc_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cancel_appr_status</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR(1)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>취소결재상태</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>company_id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(80)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEDIUMINT(5)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>테넌트ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A01:출근
+A02:지각
+A03:퇴근
+A07:휴근
+A04:외근
+A06:외출
+A05:휴가
+A09:출장
+A10:파견
+A08:조퇴
+A17:결근
+A11:연차
+A12:오전반차
+A13:오후반차
+A14:공가
+A15:오전공가
+A16:오후공가
+A18:산휴
+A19:경조
+A20:병가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1754,8 +2352,20 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1766,6 +2376,11 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3D3D3"/>
       </patternFill>
     </fill>
   </fills>
@@ -1844,7 +2459,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1944,11 +2559,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2231,21 +2866,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
     <col min="2" max="2" width="23.375" customWidth="1"/>
     <col min="3" max="3" width="32.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
@@ -2256,7 +2891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>21</v>
       </c>
@@ -2267,7 +2902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -2278,7 +2913,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -2289,7 +2924,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
@@ -2300,7 +2935,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
@@ -2311,7 +2946,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
@@ -2322,7 +2957,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>35</v>
       </c>
@@ -2333,7 +2968,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
@@ -2344,7 +2979,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -2355,7 +2990,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
@@ -2366,7 +3001,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
         <v>44</v>
       </c>
@@ -2377,7 +3012,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -2388,7 +3023,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
         <v>48</v>
       </c>
@@ -2399,7 +3034,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
@@ -2410,7 +3045,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
         <v>53</v>
       </c>
@@ -2421,7 +3056,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="3" t="s">
         <v>55</v>
       </c>
@@ -2432,7 +3067,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
@@ -2443,7 +3078,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
         <v>59</v>
       </c>
@@ -2454,7 +3089,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
         <v>61</v>
       </c>
@@ -2465,7 +3100,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
         <v>64</v>
       </c>
@@ -2476,7 +3111,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
         <v>66</v>
       </c>
@@ -2487,7 +3122,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
         <v>69</v>
       </c>
@@ -2498,7 +3133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
         <v>71</v>
       </c>
@@ -2509,7 +3144,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
         <v>73</v>
       </c>
@@ -2520,7 +3155,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
         <v>75</v>
       </c>
@@ -2531,7 +3166,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
         <v>77</v>
       </c>
@@ -2542,7 +3177,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
         <v>79</v>
       </c>
@@ -2553,7 +3188,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
         <v>81</v>
       </c>
@@ -2564,7 +3199,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
         <v>83</v>
       </c>
@@ -2575,7 +3210,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="3" t="s">
         <v>86</v>
       </c>
@@ -2586,7 +3221,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="3" t="s">
         <v>89</v>
       </c>
@@ -2597,7 +3232,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
         <v>92</v>
       </c>
@@ -2608,7 +3243,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" s="5" t="s">
         <v>95</v>
       </c>
@@ -2619,7 +3254,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="5" t="s">
         <v>97</v>
       </c>
@@ -2630,7 +3265,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="5" t="s">
         <v>100</v>
       </c>
@@ -2641,7 +3276,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="5" t="s">
         <v>102</v>
       </c>
@@ -2652,7 +3287,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="5" t="s">
         <v>105</v>
       </c>
@@ -2663,7 +3298,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="5" t="s">
         <v>108</v>
       </c>
@@ -2674,7 +3309,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="5" t="s">
         <v>111</v>
       </c>
@@ -2685,7 +3320,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" s="5" t="s">
         <v>113</v>
       </c>
@@ -2696,7 +3331,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" s="5" t="s">
         <v>115</v>
       </c>
@@ -2707,7 +3342,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" s="5" t="s">
         <v>118</v>
       </c>
@@ -2718,7 +3353,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" s="5" t="s">
         <v>121</v>
       </c>
@@ -2741,21 +3376,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C85"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="58.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="8" t="s">
         <v>126</v>
       </c>
@@ -2766,7 +3401,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="7" t="s">
         <v>129</v>
       </c>
@@ -2777,7 +3412,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="7" t="s">
         <v>132</v>
       </c>
@@ -2788,7 +3423,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="7" t="s">
         <v>135</v>
       </c>
@@ -2799,7 +3434,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="7" t="s">
         <v>138</v>
       </c>
@@ -2810,7 +3445,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="7" t="s">
         <v>31</v>
       </c>
@@ -2821,7 +3456,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
         <v>142</v>
       </c>
@@ -2832,7 +3467,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="7" t="s">
         <v>144</v>
       </c>
@@ -2843,7 +3478,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="7" t="s">
         <v>147</v>
       </c>
@@ -2854,7 +3489,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="7" t="s">
         <v>149</v>
       </c>
@@ -2865,7 +3500,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="7" t="s">
         <v>46</v>
       </c>
@@ -2876,7 +3511,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -2887,7 +3522,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="7" t="s">
         <v>154</v>
       </c>
@@ -2898,7 +3533,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="7" t="s">
         <v>157</v>
       </c>
@@ -2909,7 +3544,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="7" t="s">
         <v>160</v>
       </c>
@@ -2920,7 +3555,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="7" t="s">
         <v>163</v>
       </c>
@@ -2931,7 +3566,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
@@ -2942,7 +3577,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
         <v>15</v>
       </c>
@@ -2953,7 +3588,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
         <v>14</v>
       </c>
@@ -2964,7 +3599,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
         <v>16</v>
       </c>
@@ -2975,7 +3610,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="7" t="s">
         <v>57</v>
       </c>
@@ -2986,7 +3621,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
@@ -2997,7 +3632,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="7" t="s">
         <v>61</v>
       </c>
@@ -3008,7 +3643,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="7" t="s">
         <v>46</v>
       </c>
@@ -3019,7 +3654,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="7" t="s">
         <v>11</v>
       </c>
@@ -3030,7 +3665,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="7" t="s">
         <v>178</v>
       </c>
@@ -3041,7 +3676,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="7" t="s">
         <v>181</v>
       </c>
@@ -3052,7 +3687,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="7" t="s">
         <v>184</v>
       </c>
@@ -3063,7 +3698,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="7" t="s">
         <v>187</v>
       </c>
@@ -3074,7 +3709,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="9" t="s">
         <v>190</v>
       </c>
@@ -3085,7 +3720,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="9" t="s">
         <v>193</v>
       </c>
@@ -3096,7 +3731,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="9" t="s">
         <v>196</v>
       </c>
@@ -3107,7 +3742,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="9" t="s">
         <v>199</v>
       </c>
@@ -3118,7 +3753,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" s="9" t="s">
         <v>202</v>
       </c>
@@ -3129,7 +3764,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="9" t="s">
         <v>204</v>
       </c>
@@ -3140,7 +3775,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="9" t="s">
         <v>207</v>
       </c>
@@ -3151,7 +3786,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="9" t="s">
         <v>210</v>
       </c>
@@ -3162,7 +3797,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="9" t="s">
         <v>213</v>
       </c>
@@ -3173,7 +3808,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="9" t="s">
         <v>216</v>
       </c>
@@ -3184,7 +3819,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="9" t="s">
         <v>11</v>
       </c>
@@ -3195,7 +3830,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" s="9" t="s">
         <v>221</v>
       </c>
@@ -3206,7 +3841,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" s="9" t="s">
         <v>224</v>
       </c>
@@ -3217,7 +3852,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" s="9" t="s">
         <v>226</v>
       </c>
@@ -3228,7 +3863,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" s="9" t="s">
         <v>207</v>
       </c>
@@ -3239,7 +3874,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" s="9" t="s">
         <v>210</v>
       </c>
@@ -3250,7 +3885,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" s="9" t="s">
         <v>213</v>
       </c>
@@ -3261,7 +3896,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" s="9" t="s">
         <v>231</v>
       </c>
@@ -3272,7 +3907,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
         <v>226</v>
       </c>
@@ -3283,7 +3918,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" s="9" t="s">
         <v>233</v>
       </c>
@@ -3294,7 +3929,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
         <v>207</v>
       </c>
@@ -3305,7 +3940,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
         <v>48</v>
       </c>
@@ -3316,7 +3951,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
         <v>233</v>
       </c>
@@ -3327,7 +3962,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" s="9" t="s">
         <v>207</v>
       </c>
@@ -3338,7 +3973,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
         <v>163</v>
       </c>
@@ -3349,7 +3984,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
         <v>237</v>
       </c>
@@ -3360,7 +3995,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
         <v>240</v>
       </c>
@@ -3371,7 +4006,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
         <v>226</v>
       </c>
@@ -3382,7 +4017,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" s="9" t="s">
         <v>207</v>
       </c>
@@ -3393,7 +4028,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
         <v>242</v>
       </c>
@@ -3404,7 +4039,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" s="9" t="s">
         <v>244</v>
       </c>
@@ -3415,7 +4050,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
         <v>233</v>
       </c>
@@ -3426,7 +4061,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63" s="9" t="s">
         <v>163</v>
       </c>
@@ -3437,7 +4072,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64" s="9" t="s">
         <v>237</v>
       </c>
@@ -3448,7 +4083,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" s="9" t="s">
         <v>64</v>
       </c>
@@ -3459,7 +4094,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" s="9" t="s">
         <v>248</v>
       </c>
@@ -3470,7 +4105,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" s="9" t="s">
         <v>251</v>
       </c>
@@ -3481,7 +4116,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3">
       <c r="A68" s="9" t="s">
         <v>254</v>
       </c>
@@ -3492,7 +4127,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" s="9" t="s">
         <v>207</v>
       </c>
@@ -3503,7 +4138,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" s="9" t="s">
         <v>92</v>
       </c>
@@ -3514,7 +4149,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3">
       <c r="A71" s="9" t="s">
         <v>233</v>
       </c>
@@ -3525,7 +4160,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3">
       <c r="A72" s="9" t="s">
         <v>258</v>
       </c>
@@ -3536,7 +4171,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="A73" s="9" t="s">
         <v>261</v>
       </c>
@@ -3547,7 +4182,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="A74" s="9" t="s">
         <v>264</v>
       </c>
@@ -3558,7 +4193,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="A75" s="9" t="s">
         <v>267</v>
       </c>
@@ -3569,7 +4204,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3">
       <c r="A76" s="9" t="s">
         <v>270</v>
       </c>
@@ -3580,7 +4215,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3">
       <c r="A77" s="9" t="s">
         <v>273</v>
       </c>
@@ -3591,7 +4226,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3">
       <c r="A78" s="9" t="s">
         <v>207</v>
       </c>
@@ -3602,7 +4237,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3">
       <c r="A79" s="9" t="s">
         <v>92</v>
       </c>
@@ -3613,7 +4248,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3">
       <c r="A80" s="9" t="s">
         <v>226</v>
       </c>
@@ -3624,7 +4259,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3">
       <c r="A81" s="9" t="s">
         <v>258</v>
       </c>
@@ -3635,7 +4270,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3">
       <c r="A82" s="9" t="s">
         <v>261</v>
       </c>
@@ -3646,7 +4281,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3">
       <c r="A83" s="9" t="s">
         <v>264</v>
       </c>
@@ -3657,7 +4292,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3">
       <c r="A84" s="9" t="s">
         <v>267</v>
       </c>
@@ -3668,7 +4303,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3">
       <c r="A85" s="9" t="s">
         <v>270</v>
       </c>
@@ -3691,7 +4326,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I158"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="22.25" customWidth="1"/>
@@ -3700,77 +4335,77 @@
     <col min="9" max="9" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="38"/>
       <c r="C2" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="33" t="s">
+      <c r="F2" s="39"/>
+      <c r="G2" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="33"/>
+      <c r="H2" s="38"/>
       <c r="I2" s="12" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34" t="s">
+      <c r="E3" s="38"/>
+      <c r="F3" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="13" t="s">
         <v>290</v>
       </c>
@@ -3799,7 +4434,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" s="12">
         <v>1</v>
       </c>
@@ -3824,7 +4459,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" s="12">
         <v>2</v>
       </c>
@@ -3847,7 +4482,7 @@
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" s="12">
         <v>3</v>
       </c>
@@ -3870,7 +4505,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="12">
         <v>4</v>
       </c>
@@ -3893,7 +4528,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="12">
         <v>5</v>
       </c>
@@ -3916,7 +4551,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" s="15">
         <v>6</v>
       </c>
@@ -3937,7 +4572,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" s="15">
         <v>7</v>
       </c>
@@ -3958,7 +4593,7 @@
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" s="12">
         <v>8</v>
       </c>
@@ -3985,7 +4620,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" s="12">
         <v>9</v>
       </c>
@@ -4008,7 +4643,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" s="12">
         <v>10</v>
       </c>
@@ -4031,7 +4666,7 @@
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" s="12">
         <v>11</v>
       </c>
@@ -4054,7 +4689,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="12">
         <v>12</v>
       </c>
@@ -4077,7 +4712,7 @@
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="12">
         <v>13</v>
       </c>
@@ -4100,7 +4735,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="25" customFormat="1">
       <c r="A19" s="15">
         <v>14</v>
       </c>
@@ -4125,7 +4760,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" s="12">
         <v>15</v>
       </c>
@@ -4146,79 +4781,81 @@
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="33" t="s">
+      <c r="I20" s="42" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B23" s="33"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="33" t="s">
+      <c r="F23" s="39"/>
+      <c r="G23" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="H23" s="33"/>
+      <c r="H23" s="38"/>
       <c r="I23" s="12" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="33" t="s">
+    <row r="24" spans="1:9">
+      <c r="A24" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="B24" s="33"/>
+      <c r="B24" s="38"/>
       <c r="C24" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34" t="s">
+      <c r="E24" s="38"/>
+      <c r="F24" s="39" t="s">
         <v>409</v>
       </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="33" t="s">
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="34" t="s">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39" t="s">
         <v>410</v>
       </c>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="13" t="s">
         <v>290</v>
       </c>
@@ -4247,7 +4884,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" s="12">
         <v>1</v>
       </c>
@@ -4272,7 +4909,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="12">
         <v>2</v>
       </c>
@@ -4297,7 +4934,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="12">
         <v>3</v>
       </c>
@@ -4322,7 +4959,7 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="12">
         <v>4</v>
       </c>
@@ -4345,7 +4982,7 @@
       <c r="H30" s="17"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="12">
         <v>5</v>
       </c>
@@ -4372,7 +5009,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" s="10" customFormat="1">
       <c r="A32" s="1"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -4383,77 +5020,77 @@
       <c r="H32" s="31"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="33" t="s">
+    <row r="33" spans="1:9" s="10" customFormat="1">
+      <c r="A33" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-    </row>
-    <row r="34" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="33" t="s">
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+    </row>
+    <row r="34" spans="1:9" s="10" customFormat="1">
+      <c r="A34" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="38"/>
       <c r="C34" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E34" s="34" t="s">
+      <c r="E34" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="F34" s="34"/>
-      <c r="G34" s="33" t="s">
+      <c r="F34" s="39"/>
+      <c r="G34" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="H34" s="33"/>
+      <c r="H34" s="38"/>
       <c r="I34" s="12" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="33" t="s">
+    <row r="35" spans="1:9" s="10" customFormat="1">
+      <c r="A35" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="B35" s="33"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D35" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="E35" s="33"/>
-      <c r="F35" s="34" t="s">
+      <c r="E35" s="38"/>
+      <c r="F35" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-    </row>
-    <row r="36" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="33" t="s">
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+    </row>
+    <row r="36" spans="1:9" s="10" customFormat="1">
+      <c r="A36" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="34" t="s">
+      <c r="B36" s="38"/>
+      <c r="C36" s="39" t="s">
         <v>317</v>
       </c>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-    </row>
-    <row r="37" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+    </row>
+    <row r="37" spans="1:9" s="10" customFormat="1">
       <c r="A37" s="13" t="s">
         <v>290</v>
       </c>
@@ -4482,7 +5119,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" s="10" customFormat="1">
       <c r="A38" s="12">
         <v>1</v>
       </c>
@@ -4507,7 +5144,7 @@
       <c r="H38" s="12"/>
       <c r="I38" s="12"/>
     </row>
-    <row r="39" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" s="10" customFormat="1">
       <c r="A39" s="12">
         <v>2</v>
       </c>
@@ -4532,7 +5169,7 @@
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" s="10" customFormat="1">
       <c r="A40" s="12">
         <v>3</v>
       </c>
@@ -4557,7 +5194,7 @@
       </c>
       <c r="I40" s="12"/>
     </row>
-    <row r="41" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" s="10" customFormat="1">
       <c r="A41" s="12">
         <v>4</v>
       </c>
@@ -4582,7 +5219,7 @@
       </c>
       <c r="I41" s="12"/>
     </row>
-    <row r="42" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="10" customFormat="1">
       <c r="A42" s="12">
         <v>5</v>
       </c>
@@ -4609,7 +5246,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="10" customFormat="1">
       <c r="A43" s="12">
         <v>6</v>
       </c>
@@ -4636,7 +5273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="10" customFormat="1">
       <c r="A44" s="12">
         <v>7</v>
       </c>
@@ -4663,7 +5300,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="10" customFormat="1">
       <c r="A45" s="15">
         <v>8</v>
       </c>
@@ -4684,77 +5321,77 @@
       <c r="H45" s="15"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="33" t="s">
+    <row r="47" spans="1:9">
+      <c r="A47" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="33" t="s">
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B48" s="33"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="12" t="s">
         <v>368</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E48" s="34" t="s">
+      <c r="E48" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="F48" s="34"/>
-      <c r="G48" s="33" t="s">
+      <c r="F48" s="39"/>
+      <c r="G48" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="H48" s="33"/>
+      <c r="H48" s="38"/>
       <c r="I48" s="12" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="33" t="s">
+    <row r="49" spans="1:9">
+      <c r="A49" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="B49" s="33"/>
+      <c r="B49" s="38"/>
       <c r="C49" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="D49" s="33" t="s">
+      <c r="D49" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="33"/>
-      <c r="F49" s="34" t="s">
+      <c r="E49" s="38"/>
+      <c r="F49" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="33" t="s">
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="34" t="s">
+      <c r="B50" s="38"/>
+      <c r="C50" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="39"/>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="13" t="s">
         <v>290</v>
       </c>
@@ -4783,7 +5420,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9">
       <c r="A52" s="12">
         <v>1</v>
       </c>
@@ -4808,7 +5445,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9">
       <c r="A53" s="12">
         <v>2</v>
       </c>
@@ -4833,7 +5470,7 @@
       <c r="H53" s="12"/>
       <c r="I53" s="12"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9">
       <c r="A54" s="12">
         <v>3</v>
       </c>
@@ -4856,7 +5493,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9">
       <c r="A55" s="15">
         <v>4</v>
       </c>
@@ -4879,7 +5516,7 @@
       <c r="H55" s="12"/>
       <c r="I55" s="12"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9">
       <c r="A56" s="15">
         <v>5</v>
       </c>
@@ -4902,77 +5539,77 @@
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="33" t="s">
+    <row r="58" spans="1:9">
+      <c r="A58" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B58" s="33"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="33"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="33" t="s">
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B59" s="33"/>
+      <c r="B59" s="38"/>
       <c r="C59" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E59" s="34" t="s">
+      <c r="E59" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="F59" s="34"/>
-      <c r="G59" s="33" t="s">
+      <c r="F59" s="39"/>
+      <c r="G59" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="H59" s="33"/>
+      <c r="H59" s="38"/>
       <c r="I59" s="12" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="33" t="s">
+    <row r="60" spans="1:9">
+      <c r="A60" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="B60" s="33"/>
+      <c r="B60" s="38"/>
       <c r="C60" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D60" s="33" t="s">
+      <c r="D60" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="E60" s="33"/>
-      <c r="F60" s="34" t="s">
+      <c r="E60" s="38"/>
+      <c r="F60" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="33" t="s">
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="B61" s="33"/>
-      <c r="C61" s="34" t="s">
+      <c r="B61" s="38"/>
+      <c r="C61" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="D61" s="34"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="34"/>
-      <c r="I61" s="34"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="13" t="s">
         <v>290</v>
       </c>
@@ -5001,7 +5638,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9">
       <c r="A63" s="12">
         <v>1</v>
       </c>
@@ -5026,7 +5663,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
     </row>
-    <row r="64" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="10" customFormat="1">
       <c r="A64" s="12">
         <v>2</v>
       </c>
@@ -5051,7 +5688,7 @@
       <c r="H64" s="12"/>
       <c r="I64" s="12"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9">
       <c r="A65" s="12">
         <v>3</v>
       </c>
@@ -5076,7 +5713,7 @@
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9">
       <c r="A66" s="12">
         <v>4</v>
       </c>
@@ -5101,7 +5738,7 @@
       <c r="H66" s="12"/>
       <c r="I66" s="12"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67" s="12">
         <v>5</v>
       </c>
@@ -5124,7 +5761,7 @@
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9">
       <c r="A68" s="12">
         <v>6</v>
       </c>
@@ -5147,7 +5784,7 @@
       <c r="H68" s="12"/>
       <c r="I68" s="12"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69" s="12">
         <v>7</v>
       </c>
@@ -5170,7 +5807,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70" s="12">
         <v>8</v>
       </c>
@@ -5193,7 +5830,7 @@
       <c r="H70" s="12"/>
       <c r="I70" s="12"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="A71" s="12">
         <v>9</v>
       </c>
@@ -5216,7 +5853,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9">
       <c r="A72" s="12">
         <v>10</v>
       </c>
@@ -5239,7 +5876,7 @@
       <c r="H72" s="12"/>
       <c r="I72" s="12"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9">
       <c r="A73" s="12">
         <v>11</v>
       </c>
@@ -5262,7 +5899,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9">
       <c r="A74" s="12">
         <v>12</v>
       </c>
@@ -5285,7 +5922,7 @@
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
     </row>
-    <row r="75" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" s="10" customFormat="1">
       <c r="A75" s="12">
         <v>13</v>
       </c>
@@ -5306,7 +5943,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" s="12">
         <v>14</v>
       </c>
@@ -5327,7 +5964,7 @@
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9">
       <c r="A77" s="12">
         <v>15</v>
       </c>
@@ -5354,7 +5991,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9">
       <c r="A78" s="12">
         <v>16</v>
       </c>
@@ -5377,7 +6014,7 @@
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
     </row>
-    <row r="79" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" s="10" customFormat="1">
       <c r="A79" s="12">
         <v>17</v>
       </c>
@@ -5398,7 +6035,7 @@
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
     </row>
-    <row r="80" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" s="10" customFormat="1">
       <c r="A80" s="12">
         <v>18</v>
       </c>
@@ -5425,7 +6062,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="81" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" s="10" customFormat="1">
       <c r="A81" s="12">
         <v>19</v>
       </c>
@@ -5448,7 +6085,7 @@
       <c r="H81" s="12"/>
       <c r="I81" s="17"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9">
       <c r="A82" s="12">
         <v>20</v>
       </c>
@@ -5471,7 +6108,7 @@
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9">
       <c r="A83" s="12">
         <v>21</v>
       </c>
@@ -5494,7 +6131,7 @@
       <c r="H83" s="12"/>
       <c r="I83" s="12"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9">
       <c r="A84" s="12">
         <v>22</v>
       </c>
@@ -5515,7 +6152,7 @@
       <c r="H84" s="12"/>
       <c r="I84" s="12"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -5526,77 +6163,77 @@
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A86" s="33" t="s">
+    <row r="86" spans="1:9">
+      <c r="A86" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B86" s="33"/>
-      <c r="C86" s="33"/>
-      <c r="D86" s="33"/>
-      <c r="E86" s="33"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="33"/>
-      <c r="H86" s="33"/>
-      <c r="I86" s="33"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A87" s="33" t="s">
+      <c r="B86" s="38"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="38"/>
+      <c r="G86" s="38"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38"/>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B87" s="33"/>
+      <c r="B87" s="38"/>
       <c r="C87" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D87" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E87" s="34" t="s">
+      <c r="E87" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="F87" s="34"/>
-      <c r="G87" s="33" t="s">
+      <c r="F87" s="39"/>
+      <c r="G87" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="H87" s="33"/>
+      <c r="H87" s="38"/>
       <c r="I87" s="12" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A88" s="33" t="s">
+    <row r="88" spans="1:9">
+      <c r="A88" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="B88" s="33"/>
+      <c r="B88" s="38"/>
       <c r="C88" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="D88" s="33" t="s">
+      <c r="D88" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="E88" s="33"/>
-      <c r="F88" s="34" t="s">
+      <c r="E88" s="38"/>
+      <c r="F88" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="G88" s="34"/>
-      <c r="H88" s="34"/>
-      <c r="I88" s="34"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A89" s="33" t="s">
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="B89" s="33"/>
-      <c r="C89" s="34" t="s">
+      <c r="B89" s="38"/>
+      <c r="C89" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="D89" s="34"/>
-      <c r="E89" s="34"/>
-      <c r="F89" s="34"/>
-      <c r="G89" s="34"/>
-      <c r="H89" s="34"/>
-      <c r="I89" s="34"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="39"/>
+      <c r="H89" s="39"/>
+      <c r="I89" s="39"/>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" s="13" t="s">
         <v>290</v>
       </c>
@@ -5625,7 +6262,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9">
       <c r="A91" s="12">
         <v>1</v>
       </c>
@@ -5648,7 +6285,7 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9">
       <c r="A92" s="12">
         <v>2</v>
       </c>
@@ -5673,7 +6310,7 @@
       <c r="H92" s="12"/>
       <c r="I92" s="12"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9">
       <c r="A93" s="12">
         <v>3</v>
       </c>
@@ -5696,7 +6333,7 @@
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9">
       <c r="A94" s="12">
         <v>4</v>
       </c>
@@ -5719,7 +6356,7 @@
       <c r="H94" s="12"/>
       <c r="I94" s="12"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9">
       <c r="A95" s="12">
         <v>5</v>
       </c>
@@ -5742,7 +6379,7 @@
       <c r="H95" s="12"/>
       <c r="I95" s="12"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9">
       <c r="A96" s="12">
         <v>6</v>
       </c>
@@ -5765,7 +6402,7 @@
       <c r="H96" s="12"/>
       <c r="I96" s="12"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9">
       <c r="A97" s="12">
         <v>7</v>
       </c>
@@ -5788,7 +6425,7 @@
       <c r="H97" s="12"/>
       <c r="I97" s="12"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9">
       <c r="A98" s="12">
         <v>8</v>
       </c>
@@ -5811,7 +6448,7 @@
       <c r="H98" s="12"/>
       <c r="I98" s="12"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9">
       <c r="A99" s="12">
         <v>9</v>
       </c>
@@ -5834,7 +6471,7 @@
       <c r="H99" s="12"/>
       <c r="I99" s="12"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9">
       <c r="A100" s="12">
         <v>10</v>
       </c>
@@ -5857,7 +6494,7 @@
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9">
       <c r="A101" s="12">
         <v>11</v>
       </c>
@@ -5880,7 +6517,7 @@
       <c r="H101" s="12"/>
       <c r="I101" s="12"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9">
       <c r="A102" s="12">
         <v>12</v>
       </c>
@@ -5903,7 +6540,7 @@
       <c r="H102" s="12"/>
       <c r="I102" s="12"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9">
       <c r="A103" s="12">
         <v>13</v>
       </c>
@@ -5924,7 +6561,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="12"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9">
       <c r="A104" s="12">
         <v>14</v>
       </c>
@@ -5945,7 +6582,7 @@
       <c r="H104" s="12"/>
       <c r="I104" s="12"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9">
       <c r="A105" s="12">
         <v>15</v>
       </c>
@@ -5970,7 +6607,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9">
       <c r="A106" s="12">
         <v>16</v>
       </c>
@@ -5991,7 +6628,7 @@
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9">
       <c r="A107" s="12">
         <v>17</v>
       </c>
@@ -6014,7 +6651,7 @@
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9">
       <c r="A108" s="12">
         <v>18</v>
       </c>
@@ -6037,7 +6674,7 @@
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9">
       <c r="A109" s="12">
         <v>19</v>
       </c>
@@ -6060,7 +6697,7 @@
       <c r="H109" s="12"/>
       <c r="I109" s="12"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9">
       <c r="A110" s="12">
         <v>20</v>
       </c>
@@ -6085,7 +6722,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9">
       <c r="A111" s="12">
         <v>21</v>
       </c>
@@ -6108,7 +6745,7 @@
       <c r="H111" s="12"/>
       <c r="I111" s="12"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9">
       <c r="A112" s="12">
         <v>22</v>
       </c>
@@ -6131,7 +6768,7 @@
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9">
       <c r="A113" s="12">
         <v>23</v>
       </c>
@@ -6154,7 +6791,7 @@
       <c r="H113" s="12"/>
       <c r="I113" s="12"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9">
       <c r="A114" s="12">
         <v>24</v>
       </c>
@@ -6177,7 +6814,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="12"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9">
       <c r="A115" s="12">
         <v>25</v>
       </c>
@@ -6200,7 +6837,7 @@
       <c r="H115" s="12"/>
       <c r="I115" s="12"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9">
       <c r="A116" s="12">
         <v>26</v>
       </c>
@@ -6223,7 +6860,7 @@
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9">
       <c r="A117" s="12">
         <v>27</v>
       </c>
@@ -6246,7 +6883,7 @@
       <c r="H117" s="12"/>
       <c r="I117" s="12"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9">
       <c r="A118" s="12">
         <v>28</v>
       </c>
@@ -6269,7 +6906,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="12"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9">
       <c r="A119" s="12">
         <v>29</v>
       </c>
@@ -6292,7 +6929,7 @@
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9">
       <c r="A120" s="12">
         <v>30</v>
       </c>
@@ -6315,7 +6952,7 @@
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9">
       <c r="A121" s="12">
         <v>31</v>
       </c>
@@ -6338,7 +6975,7 @@
       <c r="H121" s="12"/>
       <c r="I121" s="12"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9">
       <c r="A122" s="12">
         <v>32</v>
       </c>
@@ -6361,7 +6998,7 @@
       <c r="H122" s="12"/>
       <c r="I122" s="12"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9">
       <c r="A123" s="12">
         <v>33</v>
       </c>
@@ -6384,7 +7021,7 @@
       <c r="H123" s="12"/>
       <c r="I123" s="12"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9">
       <c r="A124" s="12">
         <v>34</v>
       </c>
@@ -6407,7 +7044,7 @@
       <c r="H124" s="12"/>
       <c r="I124" s="12"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9">
       <c r="A125" s="12">
         <v>35</v>
       </c>
@@ -6430,7 +7067,7 @@
       <c r="H125" s="12"/>
       <c r="I125" s="12"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9">
       <c r="A126" s="12">
         <v>36</v>
       </c>
@@ -6453,7 +7090,7 @@
       <c r="H126" s="12"/>
       <c r="I126" s="12"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9">
       <c r="A127" s="12">
         <v>37</v>
       </c>
@@ -6476,7 +7113,7 @@
       <c r="H127" s="12"/>
       <c r="I127" s="12"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9">
       <c r="A128" s="12">
         <v>38</v>
       </c>
@@ -6499,77 +7136,77 @@
       <c r="H128" s="12"/>
       <c r="I128" s="12"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A130" s="33" t="s">
+    <row r="130" spans="1:9">
+      <c r="A130" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B130" s="33"/>
-      <c r="C130" s="33"/>
-      <c r="D130" s="33"/>
-      <c r="E130" s="33"/>
-      <c r="F130" s="33"/>
-      <c r="G130" s="33"/>
-      <c r="H130" s="33"/>
-      <c r="I130" s="33"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A131" s="33" t="s">
+      <c r="B130" s="38"/>
+      <c r="C130" s="38"/>
+      <c r="D130" s="38"/>
+      <c r="E130" s="38"/>
+      <c r="F130" s="38"/>
+      <c r="G130" s="38"/>
+      <c r="H130" s="38"/>
+      <c r="I130" s="38"/>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B131" s="33"/>
+      <c r="B131" s="38"/>
       <c r="C131" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E131" s="34" t="s">
+      <c r="E131" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="F131" s="34"/>
-      <c r="G131" s="33" t="s">
+      <c r="F131" s="39"/>
+      <c r="G131" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="H131" s="33"/>
+      <c r="H131" s="38"/>
       <c r="I131" s="12" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A132" s="33" t="s">
+    <row r="132" spans="1:9">
+      <c r="A132" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="B132" s="33"/>
+      <c r="B132" s="38"/>
       <c r="C132" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="D132" s="33" t="s">
+      <c r="D132" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="E132" s="33"/>
-      <c r="F132" s="34" t="s">
+      <c r="E132" s="38"/>
+      <c r="F132" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="G132" s="34"/>
-      <c r="H132" s="34"/>
-      <c r="I132" s="34"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A133" s="33" t="s">
+      <c r="G132" s="39"/>
+      <c r="H132" s="39"/>
+      <c r="I132" s="39"/>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="B133" s="33"/>
-      <c r="C133" s="34" t="s">
+      <c r="B133" s="38"/>
+      <c r="C133" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="D133" s="34"/>
-      <c r="E133" s="34"/>
-      <c r="F133" s="34"/>
-      <c r="G133" s="34"/>
-      <c r="H133" s="34"/>
-      <c r="I133" s="34"/>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D133" s="39"/>
+      <c r="E133" s="39"/>
+      <c r="F133" s="39"/>
+      <c r="G133" s="39"/>
+      <c r="H133" s="39"/>
+      <c r="I133" s="39"/>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" s="13" t="s">
         <v>290</v>
       </c>
@@ -6598,7 +7235,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9">
       <c r="A135" s="15">
         <v>1</v>
       </c>
@@ -6625,7 +7262,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="136" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" s="10" customFormat="1">
       <c r="A136" s="15">
         <v>2</v>
       </c>
@@ -6652,7 +7289,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9">
       <c r="A137" s="15">
         <v>3</v>
       </c>
@@ -6677,7 +7314,7 @@
       <c r="H137" s="12"/>
       <c r="I137" s="12"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9">
       <c r="A138" s="15">
         <v>4</v>
       </c>
@@ -6702,7 +7339,7 @@
       <c r="H138" s="12"/>
       <c r="I138" s="12"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9">
       <c r="A139" s="15">
         <v>5</v>
       </c>
@@ -6725,7 +7362,7 @@
       <c r="H139" s="12"/>
       <c r="I139" s="12"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9">
       <c r="A140" s="15">
         <v>6</v>
       </c>
@@ -6748,7 +7385,7 @@
       <c r="H140" s="12"/>
       <c r="I140" s="12"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9">
       <c r="A141" s="15">
         <v>7</v>
       </c>
@@ -6775,7 +7412,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="142" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" s="10" customFormat="1">
       <c r="A142" s="15">
         <v>8</v>
       </c>
@@ -6800,7 +7437,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9">
       <c r="A143" s="15">
         <v>9</v>
       </c>
@@ -6825,7 +7462,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9">
       <c r="A144" s="15">
         <v>10</v>
       </c>
@@ -6848,7 +7485,7 @@
       <c r="H144" s="12"/>
       <c r="I144" s="12"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9">
       <c r="A145" s="15">
         <v>11</v>
       </c>
@@ -6871,7 +7508,7 @@
       <c r="H145" s="12"/>
       <c r="I145" s="12"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9">
       <c r="A146" s="15">
         <v>12</v>
       </c>
@@ -6894,77 +7531,77 @@
       <c r="H146" s="12"/>
       <c r="I146" s="12"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A148" s="33" t="s">
+    <row r="148" spans="1:9">
+      <c r="A148" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B148" s="33"/>
-      <c r="C148" s="33"/>
-      <c r="D148" s="33"/>
-      <c r="E148" s="33"/>
-      <c r="F148" s="33"/>
-      <c r="G148" s="33"/>
-      <c r="H148" s="33"/>
-      <c r="I148" s="33"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A149" s="33" t="s">
+      <c r="B148" s="38"/>
+      <c r="C148" s="38"/>
+      <c r="D148" s="38"/>
+      <c r="E148" s="38"/>
+      <c r="F148" s="38"/>
+      <c r="G148" s="38"/>
+      <c r="H148" s="38"/>
+      <c r="I148" s="38"/>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B149" s="33"/>
+      <c r="B149" s="38"/>
       <c r="C149" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E149" s="34" t="s">
+      <c r="E149" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="F149" s="34"/>
-      <c r="G149" s="33" t="s">
+      <c r="F149" s="39"/>
+      <c r="G149" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="H149" s="33"/>
+      <c r="H149" s="38"/>
       <c r="I149" s="12" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A150" s="33" t="s">
+    <row r="150" spans="1:9">
+      <c r="A150" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="B150" s="33"/>
+      <c r="B150" s="38"/>
       <c r="C150" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="D150" s="33" t="s">
+      <c r="D150" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="E150" s="33"/>
-      <c r="F150" s="34" t="s">
+      <c r="E150" s="38"/>
+      <c r="F150" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="G150" s="34"/>
-      <c r="H150" s="34"/>
-      <c r="I150" s="34"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A151" s="33" t="s">
+      <c r="G150" s="39"/>
+      <c r="H150" s="39"/>
+      <c r="I150" s="39"/>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="B151" s="33"/>
-      <c r="C151" s="34" t="s">
+      <c r="B151" s="38"/>
+      <c r="C151" s="39" t="s">
         <v>322</v>
       </c>
-      <c r="D151" s="34"/>
-      <c r="E151" s="34"/>
-      <c r="F151" s="34"/>
-      <c r="G151" s="34"/>
-      <c r="H151" s="34"/>
-      <c r="I151" s="34"/>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D151" s="39"/>
+      <c r="E151" s="39"/>
+      <c r="F151" s="39"/>
+      <c r="G151" s="39"/>
+      <c r="H151" s="39"/>
+      <c r="I151" s="39"/>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" s="13" t="s">
         <v>290</v>
       </c>
@@ -6993,7 +7630,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9">
       <c r="A153" s="12">
         <v>1</v>
       </c>
@@ -7018,7 +7655,7 @@
       <c r="H153" s="12"/>
       <c r="I153" s="12"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9">
       <c r="A154" s="12">
         <v>2</v>
       </c>
@@ -7043,7 +7680,7 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9">
       <c r="A155" s="12">
         <v>3</v>
       </c>
@@ -7066,7 +7703,7 @@
       <c r="H155" s="19"/>
       <c r="I155" s="12"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9">
       <c r="A156" s="12">
         <v>4</v>
       </c>
@@ -7089,7 +7726,7 @@
       <c r="H156" s="19"/>
       <c r="I156" s="12"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9">
       <c r="A157" s="12">
         <v>5</v>
       </c>
@@ -7112,7 +7749,7 @@
       <c r="H157" s="17"/>
       <c r="I157" s="12"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9">
       <c r="A158" s="15">
         <v>6</v>
       </c>
@@ -7214,4 +7851,2232 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J88"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="40" t="s">
+        <v>505</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="41" t="s">
+        <v>506</v>
+      </c>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="40" t="s">
+        <v>507</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="41" t="s">
+        <v>508</v>
+      </c>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="41" t="s">
+        <v>510</v>
+      </c>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="40" t="s">
+        <v>511</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="40" t="s">
+        <v>513</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>518</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="34">
+        <v>1</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>521</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I7" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="J7" s="36"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="34">
+        <v>2</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>585</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>586</v>
+      </c>
+      <c r="H8" s="34">
+        <v>0</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>587</v>
+      </c>
+      <c r="J8" s="36"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="34">
+        <v>3</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>588</v>
+      </c>
+      <c r="H9" s="34">
+        <v>0</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>589</v>
+      </c>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="34">
+        <v>4</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>590</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="H10" s="34">
+        <v>0</v>
+      </c>
+      <c r="I10" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="34">
+        <v>5</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="35" t="s">
+        <v>524</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>572</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>592</v>
+      </c>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="34">
+        <v>6</v>
+      </c>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>566</v>
+      </c>
+      <c r="H12" s="34"/>
+      <c r="I12" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="34">
+        <v>7</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>584</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="H13" s="34"/>
+      <c r="I13" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="37"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="40" t="s">
+        <v>505</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="41" t="s">
+        <v>529</v>
+      </c>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="40" t="s">
+        <v>507</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="41" t="s">
+        <v>530</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="41" t="s">
+        <v>531</v>
+      </c>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="40" t="s">
+        <v>511</v>
+      </c>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="40" t="s">
+        <v>513</v>
+      </c>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>518</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="I20" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="34">
+        <v>1</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>531</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>532</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>593</v>
+      </c>
+      <c r="I21" s="35" t="s">
+        <v>533</v>
+      </c>
+      <c r="J21" s="36"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="34">
+        <v>2</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>521</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I22" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="J22" s="36"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="34">
+        <v>3</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>534</v>
+      </c>
+      <c r="G23" s="35" t="s">
+        <v>594</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I23" s="35" t="s">
+        <v>535</v>
+      </c>
+      <c r="J23" s="36"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="34">
+        <v>4</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>536</v>
+      </c>
+      <c r="G24" s="35" t="s">
+        <v>595</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>537</v>
+      </c>
+      <c r="J24" s="36"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="34">
+        <v>5</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="G25" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="H25" s="34"/>
+      <c r="I25" s="35" t="s">
+        <v>540</v>
+      </c>
+      <c r="J25" s="36"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="34">
+        <v>6</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>541</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>542</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I26" s="35" t="s">
+        <v>543</v>
+      </c>
+      <c r="J26" s="36"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="34">
+        <v>7</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>544</v>
+      </c>
+      <c r="G27" s="35" t="s">
+        <v>521</v>
+      </c>
+      <c r="H27" s="34"/>
+      <c r="I27" s="35" t="s">
+        <v>545</v>
+      </c>
+      <c r="J27" s="36"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="34">
+        <v>8</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="G28" s="35" t="s">
+        <v>546</v>
+      </c>
+      <c r="H28" s="34"/>
+      <c r="I28" s="35" t="s">
+        <v>547</v>
+      </c>
+      <c r="J28" s="36"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="34">
+        <v>9</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="H29" s="34"/>
+      <c r="I29" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="J29" s="36"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="40" t="s">
+        <v>505</v>
+      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="41" t="s">
+        <v>548</v>
+      </c>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="40" t="s">
+        <v>507</v>
+      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="41" t="s">
+        <v>596</v>
+      </c>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="41" t="s">
+        <v>597</v>
+      </c>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="40" t="s">
+        <v>511</v>
+      </c>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="40" t="s">
+        <v>513</v>
+      </c>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>518</v>
+      </c>
+      <c r="H36" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="J36" s="33" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="34">
+        <v>1</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I37" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="J37" s="36"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="34">
+        <v>2</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E38" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="G38" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="H38" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I38" s="35" t="s">
+        <v>598</v>
+      </c>
+      <c r="J38" s="36"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="34">
+        <v>3</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E39" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>599</v>
+      </c>
+      <c r="G39" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="H39" s="34">
+        <v>1</v>
+      </c>
+      <c r="I39" s="35" t="s">
+        <v>600</v>
+      </c>
+      <c r="J39" s="36"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="34">
+        <v>4</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>601</v>
+      </c>
+      <c r="G40" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="H40" s="34">
+        <v>1</v>
+      </c>
+      <c r="I40" s="35" t="s">
+        <v>552</v>
+      </c>
+      <c r="J40" s="36"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="34">
+        <v>5</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F41" s="35" t="s">
+        <v>602</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="H41" s="34">
+        <v>1</v>
+      </c>
+      <c r="I41" s="35" t="s">
+        <v>553</v>
+      </c>
+      <c r="J41" s="36"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="34">
+        <v>6</v>
+      </c>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="35" t="s">
+        <v>554</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>603</v>
+      </c>
+      <c r="H42" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I42" s="35" t="s">
+        <v>604</v>
+      </c>
+      <c r="J42" s="36"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="34">
+        <v>7</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F43" s="35" t="s">
+        <v>605</v>
+      </c>
+      <c r="G43" s="35" t="s">
+        <v>606</v>
+      </c>
+      <c r="H43" s="34">
+        <v>1</v>
+      </c>
+      <c r="I43" s="35" t="s">
+        <v>555</v>
+      </c>
+      <c r="J43" s="36"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="34">
+        <v>8</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D44" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E44" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F44" s="35" t="s">
+        <v>556</v>
+      </c>
+      <c r="G44" s="35" t="s">
+        <v>607</v>
+      </c>
+      <c r="H44" s="34">
+        <v>1</v>
+      </c>
+      <c r="I44" s="35" t="s">
+        <v>608</v>
+      </c>
+      <c r="J44" s="36"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="34">
+        <v>9</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>609</v>
+      </c>
+      <c r="G45" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="H45" s="34">
+        <v>1</v>
+      </c>
+      <c r="I45" s="35" t="s">
+        <v>610</v>
+      </c>
+      <c r="J45" s="36"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="34">
+        <v>10</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E46" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F46" s="35" t="s">
+        <v>611</v>
+      </c>
+      <c r="G46" s="35" t="s">
+        <v>603</v>
+      </c>
+      <c r="H46" s="34"/>
+      <c r="I46" s="35" t="s">
+        <v>578</v>
+      </c>
+      <c r="J46" s="36"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="37"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="37"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="40" t="s">
+        <v>505</v>
+      </c>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="41" t="s">
+        <v>612</v>
+      </c>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="39"/>
+      <c r="J48" s="39"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="40" t="s">
+        <v>507</v>
+      </c>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="41" t="s">
+        <v>613</v>
+      </c>
+      <c r="F49" s="39"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="41" t="s">
+        <v>614</v>
+      </c>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="39"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="40" t="s">
+        <v>511</v>
+      </c>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="39"/>
+      <c r="J51" s="39"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="40" t="s">
+        <v>513</v>
+      </c>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="G53" s="33" t="s">
+        <v>518</v>
+      </c>
+      <c r="H53" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="J53" s="33" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="34">
+        <v>1</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E54" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F54" s="35" t="s">
+        <v>615</v>
+      </c>
+      <c r="G54" s="35" t="s">
+        <v>557</v>
+      </c>
+      <c r="H54" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I54" s="35" t="s">
+        <v>558</v>
+      </c>
+      <c r="J54" s="36"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="34">
+        <v>2</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E55" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>559</v>
+      </c>
+      <c r="G55" s="35" t="s">
+        <v>616</v>
+      </c>
+      <c r="H55" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I55" s="35" t="s">
+        <v>617</v>
+      </c>
+      <c r="J55" s="36"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="34">
+        <v>3</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E56" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="G56" s="35" t="s">
+        <v>618</v>
+      </c>
+      <c r="H56" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I56" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="J56" s="36"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="34">
+        <v>4</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F57" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="G57" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="H57" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I57" s="35" t="s">
+        <v>619</v>
+      </c>
+      <c r="J57" s="36"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="34">
+        <v>5</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F58" s="35" t="s">
+        <v>560</v>
+      </c>
+      <c r="G58" s="35" t="s">
+        <v>620</v>
+      </c>
+      <c r="H58" s="34"/>
+      <c r="I58" s="35" t="s">
+        <v>561</v>
+      </c>
+      <c r="J58" s="36"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="34">
+        <v>6</v>
+      </c>
+      <c r="B59" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D59" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E59" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F59" s="35" t="s">
+        <v>621</v>
+      </c>
+      <c r="G59" s="35" t="s">
+        <v>562</v>
+      </c>
+      <c r="H59" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I59" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="J59" s="36"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="34">
+        <v>7</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F60" s="35" t="s">
+        <v>622</v>
+      </c>
+      <c r="G60" s="35" t="s">
+        <v>562</v>
+      </c>
+      <c r="H60" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I60" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="J60" s="36"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="34">
+        <v>8</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D61" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F61" s="35" t="s">
+        <v>565</v>
+      </c>
+      <c r="G61" s="35" t="s">
+        <v>623</v>
+      </c>
+      <c r="H61" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I61" s="35" t="s">
+        <v>624</v>
+      </c>
+      <c r="J61" s="36"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="34">
+        <v>9</v>
+      </c>
+      <c r="B62" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F62" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="G62" s="35" t="s">
+        <v>566</v>
+      </c>
+      <c r="H62" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I62" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="J62" s="36"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="34">
+        <v>10</v>
+      </c>
+      <c r="B63" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C63" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E63" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F63" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="G63" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="H63" s="34"/>
+      <c r="I63" s="35" t="s">
+        <v>627</v>
+      </c>
+      <c r="J63" s="36"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="34">
+        <v>11</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E64" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F64" s="35" t="s">
+        <v>628</v>
+      </c>
+      <c r="G64" s="35" t="s">
+        <v>562</v>
+      </c>
+      <c r="H64" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I64" s="35" t="s">
+        <v>629</v>
+      </c>
+      <c r="J64" s="36"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="34">
+        <v>12</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E65" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F65" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="G65" s="35" t="s">
+        <v>630</v>
+      </c>
+      <c r="H65" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I65" s="35" t="s">
+        <v>631</v>
+      </c>
+      <c r="J65" s="36"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="34">
+        <v>13</v>
+      </c>
+      <c r="B66" s="34"/>
+      <c r="C66" s="34"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="35" t="s">
+        <v>570</v>
+      </c>
+      <c r="G66" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="H66" s="34">
+        <v>0</v>
+      </c>
+      <c r="I66" s="35"/>
+      <c r="J66" s="36"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="34">
+        <v>14</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E67" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F67" s="35" t="s">
+        <v>632</v>
+      </c>
+      <c r="G67" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="H67" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I67" s="35" t="s">
+        <v>633</v>
+      </c>
+      <c r="J67" s="36"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="34">
+        <v>15</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D68" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E68" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F68" s="35" t="s">
+        <v>571</v>
+      </c>
+      <c r="G68" s="35" t="s">
+        <v>572</v>
+      </c>
+      <c r="H68" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I68" s="35" t="s">
+        <v>634</v>
+      </c>
+      <c r="J68" s="36"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="34">
+        <v>16</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D69" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E69" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F69" s="35" t="s">
+        <v>635</v>
+      </c>
+      <c r="G69" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="H69" s="34">
+        <v>0</v>
+      </c>
+      <c r="I69" s="35" t="s">
+        <v>573</v>
+      </c>
+      <c r="J69" s="36"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="34">
+        <v>17</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D70" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E70" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F70" s="35" t="s">
+        <v>574</v>
+      </c>
+      <c r="G70" s="35" t="s">
+        <v>636</v>
+      </c>
+      <c r="H70" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I70" s="35" t="s">
+        <v>575</v>
+      </c>
+      <c r="J70" s="36"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="34">
+        <v>18</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C71" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D71" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E71" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F71" s="35" t="s">
+        <v>637</v>
+      </c>
+      <c r="G71" s="35" t="s">
+        <v>562</v>
+      </c>
+      <c r="H71" s="34" t="s">
+        <v>638</v>
+      </c>
+      <c r="I71" s="35" t="s">
+        <v>639</v>
+      </c>
+      <c r="J71" s="36"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="34">
+        <v>19</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D72" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E72" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F72" s="35" t="s">
+        <v>576</v>
+      </c>
+      <c r="G72" s="35" t="s">
+        <v>562</v>
+      </c>
+      <c r="H72" s="34" t="s">
+        <v>640</v>
+      </c>
+      <c r="I72" s="35" t="s">
+        <v>641</v>
+      </c>
+      <c r="J72" s="36"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="34">
+        <v>20</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D73" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E73" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F73" s="35" t="s">
+        <v>577</v>
+      </c>
+      <c r="G73" s="35" t="s">
+        <v>572</v>
+      </c>
+      <c r="H73" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I73" s="35" t="s">
+        <v>578</v>
+      </c>
+      <c r="J73" s="36"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="37"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="40" t="s">
+        <v>505</v>
+      </c>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="41" t="s">
+        <v>579</v>
+      </c>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="40" t="s">
+        <v>507</v>
+      </c>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="41" t="s">
+        <v>642</v>
+      </c>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="39"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="40" t="s">
+        <v>509</v>
+      </c>
+      <c r="B77" s="39"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="41" t="s">
+        <v>643</v>
+      </c>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39"/>
+      <c r="H77" s="39"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="39"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="40" t="s">
+        <v>511</v>
+      </c>
+      <c r="B78" s="39"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="E78" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F78" s="39"/>
+      <c r="G78" s="39"/>
+      <c r="H78" s="39"/>
+      <c r="I78" s="39"/>
+      <c r="J78" s="39"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="40" t="s">
+        <v>513</v>
+      </c>
+      <c r="B79" s="39"/>
+      <c r="C79" s="39"/>
+      <c r="D79" s="39"/>
+      <c r="E79" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F79" s="39"/>
+      <c r="G79" s="39"/>
+      <c r="H79" s="39"/>
+      <c r="I79" s="39"/>
+      <c r="J79" s="39"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="B80" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="C80" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="G80" s="33" t="s">
+        <v>518</v>
+      </c>
+      <c r="H80" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="I80" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="J80" s="33" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="34">
+        <v>1</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D81" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E81" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F81" s="35" t="s">
+        <v>615</v>
+      </c>
+      <c r="G81" s="35" t="s">
+        <v>557</v>
+      </c>
+      <c r="H81" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I81" s="35" t="s">
+        <v>558</v>
+      </c>
+      <c r="J81" s="36"/>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="34">
+        <v>2</v>
+      </c>
+      <c r="B82" s="34"/>
+      <c r="C82" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D82" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E82" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F82" s="35" t="s">
+        <v>644</v>
+      </c>
+      <c r="G82" s="35" t="s">
+        <v>620</v>
+      </c>
+      <c r="H82" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I82" s="35" t="s">
+        <v>645</v>
+      </c>
+      <c r="J82" s="36"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="34">
+        <v>3</v>
+      </c>
+      <c r="B83" s="34"/>
+      <c r="C83" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D83" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E83" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F83" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="G83" s="35" t="s">
+        <v>647</v>
+      </c>
+      <c r="H83" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I83" s="35" t="s">
+        <v>580</v>
+      </c>
+      <c r="J83" s="36"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="34">
+        <v>4</v>
+      </c>
+      <c r="B84" s="34"/>
+      <c r="C84" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D84" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E84" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F84" s="35" t="s">
+        <v>648</v>
+      </c>
+      <c r="G84" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="H84" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I84" s="35" t="s">
+        <v>581</v>
+      </c>
+      <c r="J84" s="36"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="34">
+        <v>5</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D85" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E85" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F85" s="35" t="s">
+        <v>582</v>
+      </c>
+      <c r="G85" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="H85" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I85" s="35" t="s">
+        <v>583</v>
+      </c>
+      <c r="J85" s="36"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="34">
+        <v>6</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D86" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E86" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F86" s="35" t="s">
+        <v>649</v>
+      </c>
+      <c r="G86" s="35" t="s">
+        <v>650</v>
+      </c>
+      <c r="H86" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="I86" s="35" t="s">
+        <v>651</v>
+      </c>
+      <c r="J86" s="36"/>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="34">
+        <v>7</v>
+      </c>
+      <c r="B87" s="34" t="s">
+        <v>584</v>
+      </c>
+      <c r="C87" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D87" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E87" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F87" s="35" t="s">
+        <v>652</v>
+      </c>
+      <c r="G87" s="35" t="s">
+        <v>653</v>
+      </c>
+      <c r="H87" s="34"/>
+      <c r="I87" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="J87" s="36"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="34">
+        <v>8</v>
+      </c>
+      <c r="B88" s="34" t="s">
+        <v>654</v>
+      </c>
+      <c r="C88" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D88" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E88" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F88" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="G88" s="35" t="s">
+        <v>655</v>
+      </c>
+      <c r="H88" s="34"/>
+      <c r="I88" s="35" t="s">
+        <v>656</v>
+      </c>
+      <c r="J88" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="50">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:J15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:J18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:J19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:J31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:J33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:J34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:J35"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:J48"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E50:J50"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E51:J51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E52:J52"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="E75:J75"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="E79:J79"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="E76:J76"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="E77:J77"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="E78:J78"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>